--- a/media/exports/reports/2026-10/people-helped.xlsx
+++ b/media/exports/reports/2026-10/people-helped.xlsx
@@ -287,7 +287,21 @@
           </spPr>
           <invertIfNegative val="0"/>
           <dPt>
-            <idx val="1"/>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="7D8790"/>
@@ -428,7 +442,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.07295"/>
+          <max val="1.15"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -442,7 +456,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.07295"/>
+          <max val="1.15"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -828,7 +842,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -886,7 +900,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>September 94</t>
+          <t>September 100</t>
         </is>
       </c>
     </row>
@@ -960,7 +974,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Housing support</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
       <c r="B16" s="6">
@@ -975,7 +989,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mental health first aid</t>
+          <t>Housing support</t>
         </is>
       </c>
       <c r="B17" s="6">
@@ -1039,19 +1053,19 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Couldn't make contact</t>
+          <t>Program at capacity</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Program at capacity</t>
+          <t>Waitlist</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
@@ -1063,7 +1077,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Not eligible</t>
+          <t>Outside the service area</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -1083,7 +1097,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>78 people were helped in October so far, and 13 came to a program but couldn't be helped: 85.7% reached (target 90.0%), against 85.4% in September.</t>
+          <t>78 people were helped in October so far, and 12 came to a program but couldn't be helped: 86.7% reached (target 90.0%), against 84.6% in September.</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1112,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Youth outreach reached the smallest share: 72.0% (7 couldn't be helped). The main reason: couldn't make contact (7 people).</t>
+          <t>Mental health first aid reached the smallest share: 73.3% (4 couldn't be helped). The main reason: program at capacity (6 people).</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1129,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1160,7 +1174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1212,10 +1226,10 @@
         </is>
       </c>
       <c r="B9" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="15" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1289,10 +1303,10 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="15" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -1366,10 +1380,10 @@
         </is>
       </c>
       <c r="B27" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" s="15" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1435,7 +1449,7 @@
         </is>
       </c>
       <c r="B36" s="15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -1490,7 +1504,7 @@
         </is>
       </c>
       <c r="B44" s="15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1509,7 +1523,7 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Housing support, October 2026 to date</t>
+          <t>Mental health first aid, October 2026 to date</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1549,7 @@
         </is>
       </c>
       <c r="B51" s="15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -1545,7 +1559,7 @@
         </is>
       </c>
       <c r="B52" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -1564,7 +1578,7 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>Mental health first aid, October 2026 to date</t>
+          <t>Housing support, October 2026 to date</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1604,7 @@
         </is>
       </c>
       <c r="B59" s="15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
@@ -1600,7 +1614,7 @@
         </is>
       </c>
       <c r="B60" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1678,7 +1692,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1769,7 +1783,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1830,7 @@
         <v>211</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E6" s="19">
         <f>IF(C6+D6=0,"",C6/(C6+D6))</f>
@@ -1838,7 +1852,7 @@
         <v>195</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E7" s="19">
         <f>IF(C7+D7=0,"",C7/(C7+D7))</f>
@@ -1882,7 +1896,7 @@
         <v>297</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E9" s="19">
         <f>IF(C9+D9=0,"",C9/(C9+D9))</f>
@@ -1904,7 +1918,7 @@
         <v>278</v>
       </c>
       <c r="D10" s="15" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E10" s="19">
         <f>IF(C10+D10=0,"",C10/(C10+D10))</f>
@@ -1926,7 +1940,7 @@
         <v>314</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E11" s="19">
         <f>IF(C11+D11=0,"",C11/(C11+D11))</f>
@@ -1948,7 +1962,7 @@
         <v>305</v>
       </c>
       <c r="D12" s="15" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E12" s="19">
         <f>IF(C12+D12=0,"",C12/(C12+D12))</f>
@@ -1970,7 +1984,7 @@
         <v>265</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E13" s="19">
         <f>IF(C13+D13=0,"",C13/(C13+D13))</f>
@@ -1992,7 +2006,7 @@
         <v>425</v>
       </c>
       <c r="D14" s="15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E14" s="19">
         <f>IF(C14+D14=0,"",C14/(C14+D14))</f>
@@ -2014,7 +2028,7 @@
         <v>446</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E15" s="19">
         <f>IF(C15+D15=0,"",C15/(C15+D15))</f>
@@ -2036,7 +2050,7 @@
         <v>474</v>
       </c>
       <c r="D16" s="15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E16" s="19">
         <f>IF(C16+D16=0,"",C16/(C16+D16))</f>
@@ -2058,7 +2072,7 @@
         <v>506</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E17" s="19">
         <f>IF(C17+D17=0,"",C17/(C17+D17))</f>
@@ -2080,7 +2094,7 @@
         <v>495</v>
       </c>
       <c r="D18" s="15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="19">
         <f>IF(C18+D18=0,"",C18/(C18+D18))</f>
@@ -2102,7 +2116,7 @@
         <v>521</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E19" s="19">
         <f>IF(C19+D19=0,"",C19/(C19+D19))</f>
@@ -2124,7 +2138,7 @@
         <v>427</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E20" s="19">
         <f>IF(C20+D20=0,"",C20/(C20+D20))</f>
@@ -2146,7 +2160,7 @@
         <v>396</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" s="19">
         <f>IF(C21+D21=0,"",C21/(C21+D21))</f>
@@ -2168,7 +2182,7 @@
         <v>412</v>
       </c>
       <c r="D22" s="15" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E22" s="19">
         <f>IF(C22+D22=0,"",C22/(C22+D22))</f>
@@ -2190,7 +2204,7 @@
         <v>491</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E23" s="19">
         <f>IF(C23+D23=0,"",C23/(C23+D23))</f>
@@ -2234,7 +2248,7 @@
         <v>490</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E25" s="19">
         <f>IF(C25+D25=0,"",C25/(C25+D25))</f>
@@ -2256,7 +2270,7 @@
         <v>497</v>
       </c>
       <c r="D26" s="15" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E26" s="19">
         <f>IF(C26+D26=0,"",C26/(C26+D26))</f>
@@ -2278,7 +2292,7 @@
         <v>522</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="E27" s="19">
         <f>IF(C27+D27=0,"",C27/(C27+D27))</f>
@@ -2300,7 +2314,7 @@
         <v>548</v>
       </c>
       <c r="D28" s="15" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E28" s="19">
         <f>IF(C28+D28=0,"",C28/(C28+D28))</f>
@@ -2322,7 +2336,7 @@
         <v>78</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" s="19">
         <f>IF(C29+D29=0,"",C29/(C29+D29))</f>
@@ -2335,7 +2349,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/people-helped.xlsx
+++ b/media/exports/reports/2026-10/people-helped.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="People_helped_October_so_far">'Report'!$B$8</definedName>
-    <definedName name="Couldn_t_reach_October_so_far">'Report'!$B$9</definedName>
-    <definedName name="Share_reached_October_so_far">'Report'!$B$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$38</definedName>
+    <definedName name="People_helped_October_so_far">'Report'!$B$9</definedName>
+    <definedName name="Couldn_t_reach_October_so_far">'Report'!$B$10</definedName>
+    <definedName name="Share_reached_October_so_far">'Report'!$B$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$69</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$E$29</definedName>
@@ -55,6 +55,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -75,11 +80,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -117,26 +117,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -144,12 +147,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -338,12 +341,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$14:$A$18</f>
+              <f>'Report'!$A$15:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$14:$B$18</f>
+              <f>'Report'!$B$15:$B$19</f>
             </numRef>
           </val>
         </ser>
@@ -492,7 +495,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2286000"/>
@@ -816,7 +819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -842,7 +845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -850,293 +853,301 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: 78 people helped in October so far; 12 couldn't be reached (86.7% reached, target 90.0%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>People helped by each program, day by day, and the people who came to a program but couldn't be helped (and why). People helped are counted against each program's own grant spend.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>People helped, October so far</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>September 548</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Couldn't reach, October so far</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B19</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>September 100</t>
+          <t>People helped, October so far</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>September 548</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Couldn't reach, October so far</t>
+        </is>
+      </c>
+      <c r="B10" s="7">
+        <f>Workings!B18</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>September 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Share reached, October so far</t>
         </is>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="9">
         <f>Workings!B28</f>
         <v/>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>target 90.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Share of people reached, by program, October 2026 to date</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Share reached %</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>People helped</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Community meals</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C14" s="9">
-        <f>Workings!B36</f>
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>Workings!B45</f>
-        <v/>
-      </c>
-      <c r="C15" s="9">
-        <f>Workings!B44</f>
+          <t>Community meals</t>
+        </is>
+      </c>
+      <c r="B15" s="9">
+        <f>Workings!B37</f>
+        <v/>
+      </c>
+      <c r="C15" s="7">
+        <f>Workings!B35</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mental health first aid</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>Workings!B53</f>
-        <v/>
-      </c>
-      <c r="C16" s="9">
-        <f>Workings!B52</f>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B45</f>
+        <v/>
+      </c>
+      <c r="C16" s="7">
+        <f>Workings!B43</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Housing support</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <f>Workings!B61</f>
-        <v/>
-      </c>
-      <c r="C17" s="9">
-        <f>Workings!B60</f>
+          <t>Mental health first aid</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C17" s="7">
+        <f>Workings!B51</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Housing support</t>
+        </is>
+      </c>
+      <c r="B18" s="9">
+        <f>Workings!B61</f>
+        <v/>
+      </c>
+      <c r="C18" s="7">
+        <f>Workings!B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Digital literacy</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B19" s="9">
         <f>Workings!B69</f>
         <v/>
       </c>
-      <c r="C18" s="9">
-        <f>Workings!B68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="C19" s="7">
+        <f>Workings!B67</f>
+        <v/>
+      </c>
+    </row>
     <row r="20"/>
     <row r="21"/>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>People helped by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Why people couldn't be helped, October 2026 to date</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Main reason</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>People</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Program at capacity</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Waitlist</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Outside the service area</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>78 people were helped in October so far, and 12 came to a program but couldn't be helped: 86.7% reached (target 90.0%), against 84.6% in September.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Mental health first aid reached the smallest share: 73.3% (4 couldn't be helped). The main reason: program at capacity (6 people).</t>
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40"/>
+    <row r="41"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="27" min="0" max="16383" man="1"/>
+    <brk id="28" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1174,33 +1185,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>People helped, October and September</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1212,10 +1223,10 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>548</v>
       </c>
     </row>
@@ -1225,24 +1236,24 @@
           <t>People we couldn't reach</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="18">
         <f>B8/(B8+B9)</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <f>C8/(C8+C9)</f>
         <v/>
       </c>
@@ -1257,27 +1268,27 @@
     <row r="12"/>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>People helped, October and September</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1289,10 +1300,10 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>548</v>
       </c>
     </row>
@@ -1302,24 +1313,24 @@
           <t>People we couldn't reach</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="16" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="18">
         <f>B17/(B17+B18)</f>
         <v/>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <f>C17/(C17+C18)</f>
         <v/>
       </c>
@@ -1334,27 +1345,27 @@
     <row r="21"/>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>People helped, October and September</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
@@ -1366,10 +1377,10 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="16" t="n">
         <v>548</v>
       </c>
     </row>
@@ -1379,24 +1390,24 @@
           <t>People we couldn't reach</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="16" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="18">
         <f>B26/(B26+B27)</f>
         <v/>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="18">
         <f>C26/(C26+C27)</f>
         <v/>
       </c>
@@ -1411,22 +1422,22 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Community meals, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1438,7 +1449,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B35" s="16" t="n">
         <v>28</v>
       </c>
     </row>
@@ -1448,17 +1459,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B36" s="16" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="18">
         <f>B35/(B35+B36)</f>
         <v/>
       </c>
@@ -1466,22 +1477,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Youth outreach, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1493,7 +1504,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
+      <c r="B43" s="16" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1503,17 +1514,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
+      <c r="B44" s="16" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="18">
         <f>B43/(B43+B44)</f>
         <v/>
       </c>
@@ -1521,22 +1532,22 @@
     <row r="46"/>
     <row r="47"/>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Mental health first aid, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1548,7 +1559,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B51" s="15" t="n">
+      <c r="B51" s="16" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1558,17 +1569,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B52" s="15" t="n">
+      <c r="B52" s="16" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="18">
         <f>B51/(B51+B52)</f>
         <v/>
       </c>
@@ -1576,22 +1587,22 @@
     <row r="54"/>
     <row r="55"/>
     <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Housing support, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr"/>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1603,7 +1614,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B59" s="15" t="n">
+      <c r="B59" s="16" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1613,17 +1624,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B60" s="15" t="n">
+      <c r="B60" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="18">
         <f>B59/(B59+B60)</f>
         <v/>
       </c>
@@ -1631,22 +1642,22 @@
     <row r="62"/>
     <row r="63"/>
     <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+      <c r="A64" s="15" t="inlineStr">
         <is>
           <t>Digital literacy, October 2026 to date</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>Helped ÷ (helped + couldn't reach)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr"/>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr"/>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -1658,7 +1669,7 @@
           <t>People helped</t>
         </is>
       </c>
-      <c r="B67" s="15" t="n">
+      <c r="B67" s="16" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1668,17 +1679,17 @@
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="B68" s="15" t="n">
+      <c r="B68" s="16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="18">
         <f>B67/(B67+B68)</f>
         <v/>
       </c>
@@ -1692,7 +1703,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1783,562 +1794,562 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>People helped</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Couldn't reach</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Share reached</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>211</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>IF(C6+D6=0,"",C6/(C6+D6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>195</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>IF(C7+D7=0,"",C7/(C7+D7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>308</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>IF(C8+D8=0,"",C8/(C8+D8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>297</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>IF(C9+D9=0,"",C9/(C9+D9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>278</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>IF(C10+D10=0,"",C10/(C10+D10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>314</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>IF(C11+D11=0,"",C11/(C11+D11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>305</v>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>34</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>IF(C12+D12=0,"",C12/(C12+D12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>265</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>IF(C13+D13=0,"",C13/(C13+D13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>425</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>68</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>IF(C14+D14=0,"",C14/(C14+D14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>446</v>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>65</v>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>IF(C15+D15=0,"",C15/(C15+D15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="16" t="n">
         <v>474</v>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>IF(C16+D16=0,"",C16/(C16+D16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="16" t="n">
         <v>506</v>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D17" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>IF(C17+D17=0,"",C17/(C17+D17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="16" t="n">
         <v>495</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D18" s="16" t="n">
         <v>52</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>IF(C18+D18=0,"",C18/(C18+D18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="16" t="n">
         <v>521</v>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D19" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <f>IF(C19+D19=0,"",C19/(C19+D19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="16" t="n">
         <v>427</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="16" t="n">
         <v>49</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>IF(C20+D20=0,"",C20/(C20+D20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="16" t="n">
         <v>396</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="16" t="n">
         <v>43</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>IF(C21+D21=0,"",C21/(C21+D21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="16" t="n">
         <v>412</v>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="16" t="n">
         <v>69</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>IF(C22+D22=0,"",C22/(C22+D22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C23" s="15" t="n">
+      <c r="C23" s="16" t="n">
         <v>491</v>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="16" t="n">
         <v>93</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>IF(C23+D23=0,"",C23/(C23+D23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C24" s="15" t="n">
+      <c r="C24" s="16" t="n">
         <v>487</v>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="16" t="n">
         <v>62</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>IF(C24+D24=0,"",C24/(C24+D24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C25" s="15" t="n">
+      <c r="C25" s="16" t="n">
         <v>490</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="16" t="n">
         <v>95</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>IF(C25+D25=0,"",C25/(C25+D25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C26" s="15" t="n">
+      <c r="C26" s="16" t="n">
         <v>497</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="16" t="n">
         <v>94</v>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>IF(C26+D26=0,"",C26/(C26+D26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Aug 26</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C27" s="16" t="n">
         <v>522</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="16" t="n">
         <v>93</v>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>IF(C27+D27=0,"",C27/(C27+D27))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Sep 26</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="16" t="n">
         <v>548</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <f>IF(C28+D28=0,"",C28/(C28+D28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Oct 26</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="20">
         <f>IF(C29+D29=0,"",C29/(C29+D29))</f>
         <v/>
       </c>
@@ -2349,7 +2360,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 people-helped.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
